--- a/Team-Data/2007-08/2-23-2007-08.xlsx
+++ b/Team-Data/2007-08/2-23-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
         <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -679,31 +746,31 @@
         <v>35.2</v>
       </c>
       <c r="J2" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M2" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.336</v>
+        <v>0.333</v>
       </c>
       <c r="O2" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P2" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R2" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S2" t="n">
         <v>29.6</v>
@@ -715,7 +782,7 @@
         <v>21.2</v>
       </c>
       <c r="V2" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W2" t="n">
         <v>7.7</v>
@@ -724,7 +791,7 @@
         <v>5.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
         <v>21.4</v>
@@ -733,13 +800,13 @@
         <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -748,7 +815,7 @@
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>4</v>
@@ -769,10 +836,10 @@
         <v>29</v>
       </c>
       <c r="AN2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
         <v>8</v>
@@ -787,7 +854,7 @@
         <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="n">
         <v>20</v>
@@ -802,13 +869,13 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>9.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -954,7 +1021,7 @@
         <v>4</v>
       </c>
       <c r="AO3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
@@ -975,7 +1042,7 @@
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
@@ -984,10 +1051,10 @@
         <v>20</v>
       </c>
       <c r="AY3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
         <v>4</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -1025,55 +1092,55 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="M4" t="n">
         <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>18</v>
       </c>
       <c r="P4" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.704</v>
+        <v>0.703</v>
       </c>
       <c r="R4" t="n">
         <v>11.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T4" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U4" t="n">
         <v>21.3</v>
@@ -1082,7 +1149,7 @@
         <v>15.1</v>
       </c>
       <c r="W4" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X4" t="n">
         <v>5</v>
@@ -1091,16 +1158,16 @@
         <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
         <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.6</v>
+        <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
         <v>3</v>
@@ -1115,7 +1182,7 @@
         <v>25</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
         <v>24</v>
@@ -1151,25 +1218,25 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
         <v>17</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1297,7 +1364,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
         <v>21</v>
@@ -1324,7 +1391,7 @@
         <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1336,7 +1403,7 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
@@ -1351,7 +1418,7 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1360,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="BC5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1488,7 +1555,7 @@
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1503,13 +1570,13 @@
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>27</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1536,7 +1603,7 @@
         <v>20</v>
       </c>
       <c r="BA6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB6" t="n">
         <v>16</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1661,10 +1728,10 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ7" t="n">
         <v>26</v>
@@ -1673,7 +1740,7 @@
         <v>7</v>
       </c>
       <c r="AL7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
         <v>20</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
         <v>33</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.611</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,7 +1838,7 @@
         <v>38.8</v>
       </c>
       <c r="J8" t="n">
-        <v>85.3</v>
+        <v>85.2</v>
       </c>
       <c r="K8" t="n">
         <v>0.455</v>
@@ -1789,49 +1856,49 @@
         <v>23.3</v>
       </c>
       <c r="P8" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S8" t="n">
         <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Y8" t="n">
         <v>5.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA8" t="n">
         <v>24.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.3</v>
+        <v>107.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1855,13 +1922,13 @@
         <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
@@ -1897,7 +1964,7 @@
         <v>20</v>
       </c>
       <c r="AZ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2025,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI9" t="n">
         <v>14</v>
@@ -2034,7 +2101,7 @@
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2052,10 +2119,10 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
         <v>25</v>
@@ -2070,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2195,16 +2262,16 @@
         <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>3.6</v>
       </c>
       <c r="AD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" t="n">
         <v>8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>15</v>
@@ -2434,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>5</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2548,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>0.393</v>
+        <v>0.4</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="J12" t="n">
         <v>85.5</v>
@@ -2508,34 +2575,34 @@
         <v>8.9</v>
       </c>
       <c r="M12" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O12" t="n">
         <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S12" t="n">
         <v>32.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U12" t="n">
         <v>22.9</v>
       </c>
       <c r="V12" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W12" t="n">
         <v>7.5</v>
@@ -2550,13 +2617,13 @@
         <v>23.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD12" t="n">
         <v>3</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>8</v>
@@ -2580,7 +2647,7 @@
         <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2604,7 +2671,7 @@
         <v>17</v>
       </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2616,13 +2683,13 @@
         <v>27</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>0.358</v>
+        <v>0.365</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2684,16 +2751,16 @@
         <v>78.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
         <v>12.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.336</v>
+        <v>0.342</v>
       </c>
       <c r="O13" t="n">
         <v>21.1</v>
@@ -2702,25 +2769,25 @@
         <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.793</v>
+        <v>0.794</v>
       </c>
       <c r="R13" t="n">
         <v>9.4</v>
       </c>
       <c r="S13" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T13" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U13" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V13" t="n">
         <v>14.4</v>
       </c>
       <c r="W13" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X13" t="n">
         <v>5.1</v>
@@ -2729,7 +2796,7 @@
         <v>4.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
@@ -2738,10 +2805,10 @@
         <v>94.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.3</v>
+        <v>-4</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
@@ -2750,10 +2817,10 @@
         <v>22</v>
       </c>
       <c r="AG13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2771,10 +2838,10 @@
         <v>27</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AP13" t="n">
         <v>9</v>
@@ -2786,34 +2853,34 @@
         <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
@@ -2869,22 +2936,22 @@
         <v>0.48</v>
       </c>
       <c r="L14" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M14" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N14" t="n">
         <v>0.37</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R14" t="n">
         <v>10.7</v>
@@ -2893,16 +2960,16 @@
         <v>33.3</v>
       </c>
       <c r="T14" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>5.1</v>
@@ -2911,28 +2978,28 @@
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2959,10 +3026,10 @@
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>20</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO15" t="n">
         <v>16</v>
@@ -3165,7 +3232,7 @@
         <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3209,64 +3276,64 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G16" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="H16" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J16" t="n">
-        <v>77.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>0.454</v>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="N16" t="n">
         <v>0.338</v>
       </c>
       <c r="O16" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.719</v>
+        <v>0.716</v>
       </c>
       <c r="R16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="S16" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T16" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="U16" t="n">
         <v>20.2</v>
       </c>
       <c r="V16" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W16" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="X16" t="n">
         <v>4.3</v>
@@ -3275,10 +3342,10 @@
         <v>3.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB16" t="n">
         <v>93.2</v>
@@ -3287,7 +3354,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3317,13 +3384,13 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
         <v>22</v>
       </c>
       <c r="AP16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>28</v>
@@ -3332,7 +3399,7 @@
         <v>29</v>
       </c>
       <c r="AS16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
         <v>30</v>
@@ -3341,10 +3408,10 @@
         <v>21</v>
       </c>
       <c r="AV16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW16" t="n">
         <v>18</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>24</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F17" t="n">
         <v>35</v>
       </c>
       <c r="G17" t="n">
-        <v>0.375</v>
+        <v>0.364</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,7 +3476,7 @@
         <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>80.7</v>
+        <v>80.5</v>
       </c>
       <c r="K17" t="n">
         <v>0.449</v>
@@ -3424,22 +3491,22 @@
         <v>0.339</v>
       </c>
       <c r="O17" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="P17" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T17" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
@@ -3454,19 +3521,19 @@
         <v>4.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z17" t="n">
         <v>21.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>95</v>
+        <v>94.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.5</v>
+        <v>-6.7</v>
       </c>
       <c r="AD17" t="n">
         <v>3</v>
@@ -3478,13 +3545,13 @@
         <v>24</v>
       </c>
       <c r="AG17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ17" t="n">
         <v>16</v>
@@ -3496,7 +3563,7 @@
         <v>22</v>
       </c>
       <c r="AM17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN17" t="n">
         <v>23</v>
@@ -3505,19 +3572,19 @@
         <v>25</v>
       </c>
       <c r="AP17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
       </c>
       <c r="AT17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU17" t="n">
         <v>19</v>
@@ -3532,7 +3599,7 @@
         <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ17" t="n">
         <v>19</v>
@@ -3541,10 +3608,10 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3678,10 +3745,10 @@
         <v>24</v>
       </c>
       <c r="AM18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3690,7 +3757,7 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3708,7 +3775,7 @@
         <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3822,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>31</v>
       </c>
       <c r="G19" t="n">
-        <v>0.446</v>
+        <v>0.436</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I19" t="n">
         <v>34.1</v>
@@ -3776,34 +3843,34 @@
         <v>77.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="O19" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P19" t="n">
         <v>28</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.726</v>
+        <v>0.724</v>
       </c>
       <c r="R19" t="n">
         <v>11.6</v>
       </c>
       <c r="S19" t="n">
-        <v>31.1</v>
+        <v>30.8</v>
       </c>
       <c r="T19" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U19" t="n">
         <v>23.8</v>
@@ -3827,10 +3894,10 @@
         <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.9</v>
+        <v>-5.1</v>
       </c>
       <c r="AD19" t="n">
         <v>3</v>
@@ -3839,13 +3906,13 @@
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3863,7 +3930,7 @@
         <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3872,16 +3939,16 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AU19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -3937,94 +4004,94 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" t="n">
         <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.46</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M20" t="n">
         <v>20.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O20" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R20" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
         <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF20" t="n">
         <v>3</v>
       </c>
       <c r="AG20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH20" t="n">
         <v>6</v>
@@ -4057,16 +4124,16 @@
         <v>7</v>
       </c>
       <c r="AR20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS20" t="n">
         <v>14</v>
       </c>
-      <c r="AS20" t="n">
-        <v>15</v>
-      </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4075,7 +4142,7 @@
         <v>10</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
         <v>9</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4269,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -4382,10 +4449,10 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
@@ -4421,13 +4488,13 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>22</v>
@@ -4439,7 +4506,7 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
         <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>0.439</v>
+        <v>0.429</v>
       </c>
       <c r="H23" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I23" t="n">
         <v>36.6</v>
@@ -4504,7 +4571,7 @@
         <v>80.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
@@ -4513,7 +4580,7 @@
         <v>11.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
         <v>18.1</v>
@@ -4525,19 +4592,19 @@
         <v>0.703</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S23" t="n">
-        <v>29.1</v>
+        <v>29</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U23" t="n">
         <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W23" t="n">
         <v>8.4</v>
@@ -4549,19 +4616,19 @@
         <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA23" t="n">
         <v>20.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>95</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>18</v>
@@ -4570,10 +4637,10 @@
         <v>20</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>12</v>
@@ -4603,10 +4670,10 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT23" t="n">
         <v>16</v>
@@ -4615,7 +4682,7 @@
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>5</v>
@@ -4633,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>5.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
       </c>
       <c r="AF24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
         <v>18</v>
@@ -4779,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
         <v>5</v>
@@ -4788,7 +4855,7 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4940,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
@@ -4949,7 +5016,7 @@
         <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>18</v>
@@ -4964,16 +5031,16 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU25" t="n">
         <v>18</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
@@ -5122,7 +5189,7 @@
         <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
@@ -5137,7 +5204,7 @@
         <v>17</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5155,7 +5222,7 @@
         <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5167,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5211,22 +5278,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F27" t="n">
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J27" t="n">
         <v>78.3</v>
@@ -5241,22 +5308,22 @@
         <v>21</v>
       </c>
       <c r="N27" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O27" t="n">
         <v>16.6</v>
       </c>
       <c r="P27" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.76</v>
+        <v>0.756</v>
       </c>
       <c r="R27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T27" t="n">
         <v>41.4</v>
@@ -5280,28 +5347,28 @@
         <v>18.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC27" t="n">
         <v>5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
         <v>22</v>
@@ -5310,7 +5377,7 @@
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
         <v>5</v>
@@ -5319,7 +5386,7 @@
         <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO27" t="n">
         <v>27</v>
@@ -5328,10 +5395,10 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5358,13 +5425,13 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB27" t="n">
         <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5513,7 +5580,7 @@
         <v>11</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>1</v>
@@ -5522,7 +5589,7 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV28" t="n">
         <v>28</v>
@@ -5546,7 +5613,7 @@
         <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5665,7 +5732,7 @@
         <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5710,7 +5777,7 @@
         <v>2</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
         <v>28</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
         <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>39.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.492</v>
@@ -5787,49 +5854,49 @@
         <v>12.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.361</v>
+        <v>0.362</v>
       </c>
       <c r="O30" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="R30" t="n">
         <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
         <v>26.3</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y30" t="n">
         <v>5.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.5</v>
+        <v>105.6</v>
       </c>
       <c r="AC30" t="n">
         <v>5.8</v>
@@ -5838,7 +5905,7 @@
         <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5847,7 +5914,7 @@
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
@@ -5865,13 +5932,13 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
         <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
         <v>17</v>
@@ -5880,7 +5947,7 @@
         <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT30" t="n">
         <v>23</v>
@@ -5895,7 +5962,7 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.473</v>
+        <v>0.463</v>
       </c>
       <c r="H31" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J31" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
         <v>0.443</v>
@@ -5966,40 +6033,40 @@
         <v>6.6</v>
       </c>
       <c r="M31" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.341</v>
+        <v>0.34</v>
       </c>
       <c r="O31" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P31" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.796</v>
       </c>
       <c r="R31" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="S31" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="T31" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V31" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>4.4</v>
@@ -6011,16 +6078,16 @@
         <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF31" t="n">
         <v>17</v>
@@ -6032,7 +6099,7 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
@@ -6047,7 +6114,7 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6062,7 +6129,7 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6077,7 +6144,7 @@
         <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-23-2007-08</t>
+          <t>2008-02-23</t>
         </is>
       </c>
     </row>
